--- a/グラフクイズ用問題文作成.xlsx
+++ b/グラフクイズ用問題文作成.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/380ca7f1f0a7ae1b/デスクトップ/QC_game/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genti\OneDrive\デスクトップ\QC_game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{2D363E05-7671-4442-BE45-73FD92B16A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C5B5A1-7634-456B-A091-6A2AD840F903}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E98534-BC1B-40F2-BA21-6449A82E9B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A9A0A390-F8CC-4135-AFC3-96ED1A43FD20}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{A9A0A390-F8CC-4135-AFC3-96ED1A43FD20}"/>
   </bookViews>
   <sheets>
     <sheet name="選択ボタン" sheetId="1" r:id="rId1"/>
     <sheet name="問題１" sheetId="2" r:id="rId2"/>
-    <sheet name="問題用シート" sheetId="3" r:id="rId3"/>
+    <sheet name="正解画面" sheetId="4" r:id="rId3"/>
+    <sheet name="問題用シート" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>月</t>
     <rPh sb="0" eb="1">
@@ -69,6 +70,45 @@
     <t>気温</t>
     <rPh sb="0" eb="2">
       <t>キオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0~5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6~10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11~15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16~20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21~25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26~30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31~35</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36~40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>度数</t>
+    <rPh sb="0" eb="2">
+      <t>ドスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -100,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -109,9 +149,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -123,24 +161,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -151,6 +336,2837 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>折れ線グラフ</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>問題用シート!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>気温</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>問題用シート!$B$3:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>問題用シート!$C$3:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.94</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.82</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.03</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29.89</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-17EB-4B73-A779-0A293B85D4C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1555457472"/>
+        <c:axId val="1555455552"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1555457472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1555455552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1555455552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1555457472"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>円グラフ</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>問題用シート!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>気温</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>問題用シート!$B$3:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>問題用シート!$C$3:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.94</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.82</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.03</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29.89</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB6C-48E3-BA33-303C44C1B9F5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>ヒストグラム</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.5846842674077509E-2"/>
+          <c:y val="0.1706086956521739"/>
+          <c:w val="0.87820544490762187"/>
+          <c:h val="0.69537236106356271"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>問題用シート!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>度数</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>問題用シート!$E$3:$E$10</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0~5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6~10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11~15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16~20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21~25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26~30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31~35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36~40</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>問題用シート!$F$3:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F092-4D6D-92CC-38BDDD440197}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="1152092368"/>
+        <c:axId val="1152090448"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1152092368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1152090448"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1152090448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1152092368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -933,6 +3949,442 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5411793B-5E73-4F84-86CF-E7ED90C60462}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3219450" y="114300"/>
+          <a:ext cx="4305300" cy="4286250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="グラフ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3004DFF-FF0F-46AC-8839-10D2041B44A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165101</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>59113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>163137</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7794AC02-32B0-4073-B588-9EA587122539}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3416301" y="821113"/>
+          <a:ext cx="3898900" cy="2199524"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1415772" cy="600421"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1638992B-4435-0194-5EF9-2002776D53A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4635500" y="127000"/>
+          <a:ext cx="1415772" cy="600421"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>○正解○</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4EE9D3-0D5E-41B4-B163-306785ABF0F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3416300" y="3155950"/>
+          <a:ext cx="3886200" cy="1181100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>解説）</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>時間の経過による変化を表すデータです。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>折れ線グラフは増減や傾向を一目で把握できます。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="グラフ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0420342-819B-4701-89FB-4850CB02C7B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="グラフ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8687D31D-3B87-48AB-AB2A-852D5E38D101}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E6405AD-C69D-44A3-838D-BD9AEC6D62DA}" name="テーブル1" displayName="テーブル1" ref="B2:C14" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+  <autoFilter ref="B2:C14" xr:uid="{9E6405AD-C69D-44A3-838D-BD9AEC6D62DA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C14">
+    <sortCondition ref="C2:C14"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9A272B82-6E3B-48A5-A5AF-F1C912BD09DC}" name="月" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D2C2E1FC-10E6-40C2-AF47-70979AC4B56C}" name="気温" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -1271,121 +4723,189 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F402335-AB3C-4DA8-828C-FC86B0B8F663}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DBA61B5-74C8-418F-9DAE-998346AE19FB}">
-  <dimension ref="B1:C14"/>
+  <dimension ref="B1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.81</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="1">
-        <v>1</v>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="1">
+        <v>12</v>
       </c>
-      <c r="C3" s="1">
-        <v>6.81</v>
+      <c r="C5" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="1">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>11.94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
-        <v>5.7</v>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>14.82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="1">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>16.190000000000001</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="C5" s="1">
-        <v>11.94</v>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="1">
-        <v>4</v>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
+        <v>10</v>
       </c>
-      <c r="C6" s="1">
-        <v>16.190000000000001</v>
+      <c r="C10" s="2">
+        <v>22.35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>19.649999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="1">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C11" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="1">
-        <v>7</v>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
+        <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <v>30.02</v>
+      <c r="C12" s="2">
+        <v>28.03</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="1">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C13" s="2">
         <v>29.89</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="1">
-        <v>9</v>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B14" s="5">
+        <v>7</v>
       </c>
-      <c r="C11" s="1">
-        <v>28.03</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="1">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1">
-        <v>22.35</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="1">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1">
-        <v>14.82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="1">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1">
-        <v>10.4</v>
+      <c r="C14" s="6">
+        <v>30.02</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>